--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61D632F8-31B1-4489-B6ED-4B823726A387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91779C1E-4E8C-4E34-8963-2FEA1C803511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -1231,9 +1231,7 @@
       <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
@@ -1257,9 +1255,7 @@
       <c r="E4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
         <v>10</v>
       </c>
@@ -1283,9 +1279,7 @@
       <c r="E5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
         <v>10</v>
       </c>
@@ -1309,9 +1303,7 @@
       <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1335,9 +1327,7 @@
       <c r="E7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
         <v>10</v>
       </c>
@@ -1361,9 +1351,7 @@
       <c r="E8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1387,9 +1375,7 @@
       <c r="E9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
         <v>10</v>
       </c>
@@ -1413,9 +1399,7 @@
       <c r="E10" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
         <v>10</v>
       </c>
@@ -1439,9 +1423,7 @@
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F11" s="4"/>
       <c r="G11" s="4" t="s">
         <v>10</v>
       </c>
@@ -1465,9 +1447,7 @@
       <c r="E12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
         <v>10</v>
       </c>
@@ -1491,9 +1471,7 @@
       <c r="E13" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
         <v>10</v>
       </c>
@@ -1517,9 +1495,7 @@
       <c r="E14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
         <v>10</v>
       </c>
@@ -1543,9 +1519,7 @@
       <c r="E15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
         <v>10</v>
       </c>
@@ -1569,9 +1543,7 @@
       <c r="E16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
         <v>10</v>
       </c>
@@ -1595,9 +1567,7 @@
       <c r="E17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
         <v>10</v>
       </c>
@@ -1621,9 +1591,7 @@
       <c r="E18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
         <v>10</v>
       </c>
@@ -1647,9 +1615,7 @@
       <c r="E19" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F19" s="4"/>
       <c r="G19" s="4" t="s">
         <v>10</v>
       </c>
@@ -1673,9 +1639,7 @@
       <c r="E20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
         <v>10</v>
       </c>
@@ -1699,9 +1663,7 @@
       <c r="E21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
         <v>10</v>
       </c>
@@ -1725,9 +1687,7 @@
       <c r="E22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
         <v>10</v>
       </c>
@@ -1751,9 +1711,7 @@
       <c r="E23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
         <v>10</v>
       </c>
@@ -1777,9 +1735,7 @@
       <c r="E24" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
         <v>10</v>
       </c>
@@ -1803,9 +1759,7 @@
       <c r="E25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
         <v>10</v>
       </c>
@@ -1829,9 +1783,7 @@
       <c r="E26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>11</v>
-      </c>
+      <c r="F26" s="4"/>
       <c r="G26" s="4" t="s">
         <v>10</v>
       </c>

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -520,6 +520,12 @@
       <c r="H4" t="str">
         <v>ÇAVUŞLU-0/1519, ÇAVUŞLU-0/3887, ÇAVUŞLU-0/86, ÇAVUŞLU-0/88, ÇAVUŞLU-9980/1, ÇAVUŞLU-9980/18, ÇAVUŞLU-9981/1, ÇAVUŞLU-9981/2, ÇAVUŞLU-9982/1, ÇAVUŞLU-9982/2, ÇAVUŞLU-9982/3, ÇAVUŞLU-9982/4, ÇAVUŞLU-9982/5, ÇAVUŞLU-9982/6, ÇAVUŞLU-9982/7, ÇAVUŞLU-9983/1, ÇAVUŞLU-9983/18, ÇAVUŞLU-9984/1, ÇAVUŞLU-9985/1, ÇAVUŞLU-9985/2, ÇAVUŞLU-9985/25, ÇAVUŞLU-9985/26, ÇAVUŞLU-9985/27, ÇAVUŞLU-9985/28, ÇAVUŞLU-9985/29, ÇAVUŞLU-9985/3, ÇAVUŞLU-9985/30, ÇAVUŞLU-9985/4, ÇAVUŞLU-9985/5, ÇAVUŞLU-9985/6, ÇAVUŞLU-9985/7, ÇAVUŞLU-9986/1, ÇAVUŞLU-9986/2, ÇAVUŞLU-9986/3, ÇAVUŞLU-9986/4, ÇAVUŞLU-9986/5</v>
       </c>
+      <c r="I4" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -552,6 +552,12 @@
       <c r="H5" t="str">
         <v>ÇAVUŞLU-1422/1, ÇAVUŞLU-1422/16, ÇAVUŞLU-1422/17, ÇAVUŞLU-1422/2, ÇAVUŞLU-1423/1, ÇAVUŞLU-1435/1, ÇAVUŞLU-1435/2, ÇAVUŞLU-1435/3, ÇAVUŞLU-1435/4, ÇAVUŞLU-1435/5, ÇAVUŞLU-1435/6, ÇAVUŞLU-1436/1, ÇAVUŞLU-1436/2, ÇAVUŞLU-1437/1, ÇAVUŞLU-1437/10, ÇAVUŞLU-1437/11, ÇAVUŞLU-1437/12, ÇAVUŞLU-1437/13, ÇAVUŞLU-1437/14, ÇAVUŞLU-1437/15, ÇAVUŞLU-1437/16, ÇAVUŞLU-1437/17, ÇAVUŞLU-1437/18, ÇAVUŞLU-1437/19, ÇAVUŞLU-1437/2, ÇAVUŞLU-1437/20, ÇAVUŞLU-1437/3, ÇAVUŞLU-1437/4, ÇAVUŞLU-1437/5, ÇAVUŞLU-1437/6, ÇAVUŞLU-1437/7, ÇAVUŞLU-1437/8, ÇAVUŞLU-1437/9, ÇAVUŞLU-1439/1, ÇAVUŞLU-1439/10, ÇAVUŞLU-1439/2, ÇAVUŞLU-1439/3, ÇAVUŞLU-1439/4, ÇAVUŞLU-1439/5, ÇAVUŞLU-1439/6, ÇAVUŞLU-1439/7, ÇAVUŞLU-1439/8, ÇAVUŞLU-1439/9, ÇAVUŞLU-1440/1, ÇAVUŞLU-1440/4, ÇAVUŞLU-1440/5, ÇAVUŞLU-1440/6, ÇAVUŞLU-1440/7, ÇAVUŞLU-1440/8, ÇAVUŞLU-1440/9, OSMANİYE-1433/1, OSMANİYE-1433/15, OSMANİYE-1433/16, OSMANİYE-1433/17, OSMANİYE-1433/18, OSMANİYE-1433/2, OSMANİYE-1433/3, OSMANİYE-1433/4, OSMANİYE-1433/5, OSMANİYE-1433/6, OSMANİYE-1433/7, OSMANİYE-1434/1, OSMANİYE-1434/10, OSMANİYE-1434/11, OSMANİYE-1434/2, OSMANİYE-1434/3, OSMANİYE-1434/4, OSMANİYE-1434/5, OSMANİYE-1434/6, OSMANİYE-1434/7, OSMANİYE-1434/8, OSMANİYE-1434/9, OSMANİYE-1438/1, OSMANİYE-1438/2, OSMANİYE-1438/3, OSMANİYE-1438/4, OSMANİYE-1438/5, OSMANİYE-1438/6, OSMANİYE-1438/7, OSMANİYE-1438/8, OSMANİYE-1438/9, OSMANİYE-1441/11, OSMANİYE-1441/12, OSMANİYE-1441/13, OSMANİYE-1441/14, OSMANİYE-1441/15, OSMANİYE-1441/16, OSMANİYE-1441/21, OSMANİYE-1441/7, OSMANİYE-1441/8, OSMANİYE-1441/9</v>
       </c>
+      <c r="I5" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -584,6 +584,12 @@
       <c r="H6" t="str">
         <v>ARPAÇSAKARLAR-10693/1, ÇAVUŞLU-2920/1, ÇAVUŞLU-2921/1, ÇAVUŞLU-2924/1, ÇAVUŞLU-2939/5, ÇAVUŞLU-2940/1</v>
       </c>
+      <c r="I6" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -616,6 +616,12 @@
       <c r="H7" t="str">
         <v>ÇAVUŞLU-0/3258, ÇAVUŞLU-0/631, ÇAVUŞLU-10778/1, ÇAVUŞLU-6924/27, ÇAVUŞLU-6924/28, ÇAVUŞLU-6924/29, ÇAVUŞLU-6924/30, ÇAVUŞLU-6924/31, ÇAVUŞLU-6924/32, ÇAVUŞLU-6925/4, ÇAVUŞLU-6925/5, ÇAVUŞLU-6925/6, ÇAVUŞLU-6926/6, ÇAVUŞLU-6926/7, ÇAVUŞLU-6926/8, ÇAVUŞLU-6927/10, ÇAVUŞLU-6927/11, ÇAVUŞLU-6927/12, ÇAVUŞLU-6927/13, ÇAVUŞLU-6927/14, ÇAVUŞLU-6927/15, ÇAVUŞLU-6927/16, ÇAVUŞLU-6927/9, ÇAVUŞLU-6928/13, ÇAVUŞLU-6928/9, ÇAVUŞLU-6935/27, ÇAVUŞLU-6935/28, ÇAVUŞLU-6935/29, ÇAVUŞLU-6935/30, ÇAVUŞLU-6936/27, ÇAVUŞLU-6936/28, ÇAVUŞLU-6936/29, ÇAVUŞLU-6936/30, ÇAVUŞLU-6936/31, ÇAVUŞLU-6936/32, ÇAVUŞLU-6936/33, ÇAVUŞLU-6936/34</v>
       </c>
+      <c r="I7" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -648,6 +648,12 @@
       <c r="H8" t="str">
         <v>ÇAVUŞLU-2876/2, ÇAVUŞLU-2877/3, ÇAVUŞLU-2877/4, ÇAVUŞLU-2879/2, ÇAVUŞLU-2885/2, ÇAVUŞLU-2885/3, ÇAVUŞLU-2885/4, ÇAVUŞLU-2886/2, ÇAVUŞLU-2887/2</v>
       </c>
+      <c r="I8" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -888,6 +888,12 @@
       <c r="H17" t="str">
         <v>ÇAVUŞLU-2876/2, ÇAVUŞLU-2877/2, ÇAVUŞLU-2877/3, ÇAVUŞLU-2877/4, ÇAVUŞLU-2878/2, ÇAVUŞLU-2879/2, ÇAVUŞLU-2880/2, ÇAVUŞLU-2885/2, ÇAVUŞLU-2885/3</v>
       </c>
+      <c r="I17" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -680,6 +680,12 @@
       <c r="H9" t="str">
         <v>ÇAVUŞLU-2920/1, ÇAVUŞLU-2921/1, ÇAVUŞLU-2924/1, ÇAVUŞLU-2927/3, ÇAVUŞLU-2928/2</v>
       </c>
+      <c r="I9" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -712,6 +712,12 @@
       <c r="H10" t="str">
         <v>ÇAVUŞLU-2901/3, ÇAVUŞLU-2921/1, ÇAVUŞLU-2927/3, ÇAVUŞLU-2928/1, ÇAVUŞLU-2928/2</v>
       </c>
+      <c r="I10" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -770,6 +770,12 @@
       <c r="H12" t="str">
         <v>ÇAVUŞLU-2879/2, ÇAVUŞLU-2880/2, ÇAVUŞLU-2881/2, ÇAVUŞLU-2882/2, ÇAVUŞLU-2883/2, ÇAVUŞLU-2884/2, ÇAVUŞLU-2885/2, ÇAVUŞLU-2885/3</v>
       </c>
+      <c r="I12" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -828,6 +828,12 @@
       <c r="H14" t="str">
         <v>ÇAVUŞLU-2876/2, ÇAVUŞLU-2877/3, ÇAVUŞLU-2879/2, ÇAVUŞLU-2883/2, ÇAVUŞLU-2884/2, ÇAVUŞLU-2885/2, ÇAVUŞLU-2885/3, ÇAVUŞLU-2885/4, ÇAVUŞLU-2886/2</v>
       </c>
+      <c r="I14" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -996,6 +996,12 @@
       <c r="H20" t="str">
         <v>ÇAVUŞLU-2876/2, ÇAVUŞLU-2877/3, ÇAVUŞLU-2878/2, ÇAVUŞLU-2879/2, ÇAVUŞLU-2880/2, ÇAVUŞLU-2883/2, ÇAVUŞLU-2884/2, ÇAVUŞLU-2885/2, ÇAVUŞLU-2885/3</v>
       </c>
+      <c r="I20" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -1028,6 +1028,12 @@
       <c r="H21" t="str">
         <v>ÇAVUŞLU-9355/12, ÇAVUŞLU-9355/19, ÇAVUŞLU-9355/20, ÇAVUŞLU-9355/23, ÇAVUŞLU-9357/10, ÇAVUŞLU-9357/11, ÇAVUŞLU-9357/12, ÇAVUŞLU-9357/13, ÇAVUŞLU-9357/14, ÇAVUŞLU-9357/15, ÇAVUŞLU-9357/16, ÇAVUŞLU-9357/17, ÇAVUŞLU-9358/21, ÇAVUŞLU-9358/22, ÇAVUŞLU-9358/23, ÇAVUŞLU-9358/24, ÇAVUŞLU-9358/25, ÇAVUŞLU-9367/12, ÇAVUŞLU-9367/13, ÇAVUŞLU-9367/14, ÇAVUŞLU-9371/10, ÇAVUŞLU-9371/6, ÇAVUŞLU-9371/7, ÇAVUŞLU-9371/8, ÇAVUŞLU-9371/9, ÇAVUŞLU-9372/16, ÇAVUŞLU-9372/17, ÇAVUŞLU-9372/18, ÇAVUŞLU-9372/19, ÇAVUŞLU-9372/20, ÇAVUŞLU-9372/21</v>
       </c>
+      <c r="I21" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -860,6 +860,12 @@
       <c r="H15" t="str">
         <v>ÇAPAR-113/2, ÇAPAR-113/3, ÇAPAR-113/4, ÇAPAR-113/5, ÇAPAR-114/1, ÇAPAR-115/1, ÇAPAR-115/2, ÇAPAR-115/3, ÇAPAR-115/4, ÇAPAR-219/4, ÇAPAR-219/5, ÇAPAR-280/1, ÇAPAR-280/2, ÇAPAR-280/3, ÇAPAR-280/6, ÇAPAR-281/3, ÇAPAR-281/4, ÇAPAR-281/5, ÇAPAR-282/1, ÇAPAR-606/1</v>
       </c>
+      <c r="I15" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -744,6 +744,12 @@
       <c r="H11" t="str">
         <v>BULUKLU-0/1095, BULUKLU-0/153, BULUKLU-0/162, BULUKLU-0/163, BULUKLU-8902/2</v>
       </c>
+      <c r="I11" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -808,6 +808,12 @@
       <c r="H13" t="str">
         <v>BULUKLU-0/1385, BULUKLU-0/153, BULUKLU-0/162, BULUKLU-0/562</v>
       </c>
+      <c r="I13" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -904,6 +904,12 @@
       <c r="H16" t="str">
         <v>KEPİRLİ-0/1735, KEPİRLİ-192/21, KEPİRLİ-192/22, KEPİRLİ-192/23, KEPİRLİ-192/25, KEPİRLİ-192/26, KEPİRLİ-192/27, KEPİRLİ-192/28, KEPİRLİ-192/38, KEPİRLİ-192/39, KEPİRLİ-192/40, KEPİRLİ-192/41, KEPİRLİ-192/42, KEPİRLİ-192/43, KEPİRLİ-192/44, KEPİRLİ-391/1, KEPİRLİ-391/2, KEPİRLİ-391/3, KEPİRLİ-391/4, KEPİRLİ-391/5</v>
       </c>
+      <c r="I16" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -1084,6 +1084,12 @@
       <c r="H22" t="str">
         <v>KARAİSALİ-10745/10, KARAİSALİ-10745/11, KARAİSALİ-10745/12, KARAİSALİ-10745/3, KARAİSALİ-10745/4, KARAİSALİ-10745/5, KARAİSALİ-10745/6, KARAİSALİ-10745/7, KARAİSALİ-10745/8, KARAİSALİ-10745/9, KARAİSALİ-111/1, KARAİSALİ-111/2, KARAİSALİ-111/3, KARAİSALİ-111/4, KARAİSALİ-112/1, KARAİSALİ-112/2, KARAİSALİ-112/3, KARAİSALİ-112/4, KARAİSALİ-112/5, KARAİSALİ-112/6, KARAİSALİ-112/7, KARAİSALİ-112/8, KARAİSALİ-113/10, KARAİSALİ-113/3, KARAİSALİ-113/4, KARAİSALİ-113/5, KARAİSALİ-113/6, KARAİSALİ-113/7, KARAİSALİ-113/8, KARAİSALİ-113/9, KARAİSALİ-116/22, KARAİSALİ-116/23, KARAİSALİ-116/24, KARAİSALİ-3927/135, KARAİSALİ-3927/56, KARAİSALİ-3927/57, KARAİSALİ-3927/58, KARAİSALİ-3927/59, KARAİSALİ-3927/60, KARAİSALİ-3927/77, KARAİSALİ-3927/78, KARAİSALİ-3927/79, KARAİSALİ-3927/80, KARAİSALİ-3927/93, KARAİSALİ-3927/94, KARAİSALİ-3927/95, KARAİSALİ-3927/96, KARAİSALİ-3927/97</v>
       </c>
+      <c r="I22" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">

--- a/THA(1. ÖNCELİK).xlsx
+++ b/THA(1. ÖNCELİK).xlsx
@@ -1116,6 +1116,12 @@
       <c r="H23" t="str">
         <v>HACIİSHAKLI-0/3206, HACIİSHAKLI-0/3207, HACIİSHAKLI-0/385, HACIİSHAKLI-0/386, HACIİSHAKLI-0/387, HACIİSHAKLI-0/4159, HIRMANLI-123/19, HIRMANLI-123/20, HIRMANLI-125/4, HIRMANLI-151/15, HIRMANLI-185/1</v>
       </c>
+      <c r="I23" t="str">
+        <v>Gönderildi</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Evet</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
